--- a/Rapid Cortex Internal Docs/Archive/RC_Pricing_Master_Guide_v3.xlsx
+++ b/Rapid Cortex Internal Docs/Archive/RC_Pricing_Master_Guide_v3.xlsx
@@ -1469,7 +1469,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX</t>
+          <t>NEXCORT IQ</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Reduces rollout risk by putting Rapid Cortex experts with agency staff.</t>
+          <t xml:space="preserve">    Reduces rollout risk by putting NexCort iQ experts with agency staff.</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Helps teams understand what Rapid Cortex does vs. CAD, CPE, SOPs, and AI decision support.</t>
+          <t xml:space="preserve">    Helps teams understand what NexCort iQ does vs. CAD, CPE, SOPs, and AI decision support.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Dedicated support turns Rapid Cortex from a software vendor into an operational partner.</t>
+          <t xml:space="preserve">    Dedicated support turns NexCort iQ from a software vendor into an operational partner.</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Overages protect both the agency and Rapid Cortex by allowing flexible usage without forcing an immediate plan change.</t>
+          <t xml:space="preserve">    Overages protect both the agency and NexCort iQ by allowing flexible usage without forcing an immediate plan change.</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Smaller municipalities that want to evaluate Rapid Cortex without a full production commitment.</t>
+          <t xml:space="preserve">    Smaller municipalities that want to evaluate NexCort iQ without a full production commitment.</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sales angle: proves Rapid Cortex as a command and coordination platform.</t>
+          <t xml:space="preserve">    Sales angle: proves NexCort iQ as a command and coordination platform.</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="74" t="inlineStr">
         <is>
-          <t>RAPID CORTEX</t>
+          <t>NEXCORT IQ</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       <c r="A1" s="103" t="n"/>
       <c r="D1" s="104" t="inlineStr">
         <is>
-          <t>RAPID CORTEX</t>
+          <t>NEXCORT IQ</t>
         </is>
       </c>
       <c r="E1" s="105" t="n"/>
@@ -6406,7 +6406,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="106" t="inlineStr">
         <is>
-          <t>Apps on Demand LLC  d/b/a  Rapid Cortex  |  Intelligence at the Speed of Response</t>
+          <t>Apps on Demand LLC  d/b/a  NexCort iQ  |  Intelligence at the Speed of Response</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="129" t="inlineStr">
         <is>
-          <t>• To proceed: return signed Pilot Scope Agreement or contact your Rapid Cortex representative.</t>
+          <t>• To proceed: return signed Pilot Scope Agreement or contact your NexCort iQ representative.</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="130" t="inlineStr">
         <is>
-          <t>Rapid Cortex  |  Apps on Demand LLC  |  intelligence@rapidcortex.us  |  rapidcortex.us  |  CONFIDENTIAL — NOT FOR DISTRIBUTION</t>
+          <t>NexCort iQ  |  Apps on Demand LLC  |  intelligence@rapidcortex.us  |  rapidcortex.us  |  CONFIDENTIAL — NOT FOR DISTRIBUTION</t>
         </is>
       </c>
     </row>
@@ -7604,14 +7604,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>RAPID CORTEX ESSENTIAL</t>
+          <t>NEXCORT IQ ESSENTIAL</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -9054,14 +9054,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>RAPID CORTEX PROFESSIONAL</t>
+          <t>NEXCORT IQ PROFESSIONAL</t>
         </is>
       </c>
     </row>
@@ -10214,14 +10214,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>RAPID CORTEX COMMAND</t>
+          <t>NEXCORT IQ COMMAND</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Positions Rapid Cortex as a command and coordination platform, not just a dispatcher tool.</t>
+          <t xml:space="preserve">    Positions NexCort iQ as a command and coordination platform, not just a dispatcher tool.</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Best sales angle: Rapid Cortex becomes a long-term public safety modernization platform.</t>
+          <t xml:space="preserve">    Best sales angle: NexCort iQ becomes a long-term public safety modernization platform.</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>One-time fees · Complexity-tiered · Rapid Cortex enhances CAD — it does not replace it</t>
+          <t>One-time fees · Complexity-tiered · NexCort iQ enhances CAD — it does not replace it</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="35" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
+          <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
         </is>
       </c>
     </row>
